--- a/medical_surveys_questionnaires/046_healthcare_ethics_decision_making_survey--medical_surveys_questionnaires.xlsx
+++ b/medical_surveys_questionnaires/046_healthcare_ethics_decision_making_survey--medical_surveys_questionnaires.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Introduction</t>
+          <t>Introduction to Healthcare Ethics</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Healthcare_Professional</t>
+          <t>Healthcare Professional's Responsibility</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Patient_Career</t>
+          <t>Patient Career</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Medical_School</t>
+          <t>Medical School Training</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Hospital Environment</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Doctor</t>
+          <t>Doctor-Patient Relationship</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,7 +653,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Patient_Family</t>
+          <t>Patient Family Influence</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Patient_Status</t>
+          <t>Patient Status</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Healthcare_Institution</t>
+          <t>Healthcare Institution</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patient_Awareness</t>
+          <t>Patient Awareness</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Patient_Decision</t>
+          <t>Patient Decision-Making</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Patient_Consent</t>
+          <t>Patient Consent</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Patient_Informed</t>
+          <t>Patient Informed</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>patient_confidentiality</t>
+          <t>patient_autonomy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Patient_Confidentiality</t>
+          <t>Patient Autonomy</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>patient_privacy</t>
+          <t>patient_self_determination</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Patient_Privacy</t>
+          <t>Patient Self-Determination</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>patient_autonomy</t>
+          <t>patient_participation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Patient_Autonomy</t>
+          <t>Patient Participation</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>patient_self_determination</t>
+          <t>patient_informed_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Patient_Self_Determination</t>
+          <t>Patient Informed 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>patient_participation</t>
+          <t>patient_privacy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Patient_Participation</t>
+          <t>Patient Privacy</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>patient_informed</t>
+          <t>patient_autonomy_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Patient_Informed</t>
+          <t>Patient Autonomy 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,17 +952,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>patient_confidentiality</t>
+          <t>patient_self_determination_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Patient_Confidentiality</t>
+          <t>Patient Self Determination 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,113 +975,21 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>patient_privacy</t>
+          <t>patient_participation_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Patient_Privacy</t>
+          <t>Patient Participation 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>patient_self_determination</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Patient_Self_Determination</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>patient_participation</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Patient_Participation</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>patient_informed</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Patient_Informed</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>patient_confidentiality</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Patient_Privacy</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +1006,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>always_prioritize_patient_autonomy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Always prioritize patient autonomy</t>
         </is>
       </c>
     </row>
@@ -1148,29 +1056,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>always_prioritize_clinical_guidelines</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Always prioritize clinical guidelines</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>patient_career_choices</t>
+          <t>healthcare_professional_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>balance_between_patient_autonomy_and_clinical_guidelines</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Balance between patient autonomy and clinical guidelines</t>
         </is>
       </c>
     </row>
@@ -1182,522 +1090,522 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>important</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Important</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>medical_school_choices</t>
+          <t>patient_career_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not very important</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>medical_school_choices</t>
+          <t>patient_career_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hospital_choices</t>
+          <t>medical_school_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>sufficient</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Sufficient</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hospital_choices</t>
+          <t>medical_school_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>needs_improvement</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Needs improvement</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>doctor_choices</t>
+          <t>medical_school_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_limited</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very limited</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>doctor_choices</t>
+          <t>hospital_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>very_supportive</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Very supportive</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>patient_family_choices</t>
+          <t>hospital_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>somewhat_supportive</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Somewhat supportive</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>patient_family_choices</t>
+          <t>hospital_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>not_very_supportive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not very supportive</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>patient_status_choices</t>
+          <t>doctor_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>trustworthy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Trustworthy</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>patient_status_choices</t>
+          <t>doctor_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>somewhat_trustworthy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>Somewhat trustworthy</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>healthcare_institution_choices</t>
+          <t>doctor_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>not_very_trustworthy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not very trustworthy</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>healthcare_institution_choices</t>
+          <t>patient_family_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>very_influential</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Very influential</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>patient_awareness_choices</t>
+          <t>patient_family_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>somewhat_influential</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Somewhat influential</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>patient_awareness_choices</t>
+          <t>patient_family_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>not_very_influential</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not very influential</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>patient_decision_choices</t>
+          <t>patient_status_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>patient_decision_choices</t>
+          <t>patient_status_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>patient_consent_choices</t>
+          <t>patient_status_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not applicable</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>patient_consent_choices</t>
+          <t>healthcare_institution_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Very important</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>patient_informed_choices</t>
+          <t>healthcare_institution_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Somewhat important</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>patient_informed_choices</t>
+          <t>healthcare_institution_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not very important</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>patient_confidentiality_choices</t>
+          <t>patient_awareness_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>patient_confidentiality_choices</t>
+          <t>patient_awareness_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>patient_privacy_choices</t>
+          <t>patient_awareness_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>patient_privacy_choices</t>
+          <t>patient_decision_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>very_effective</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Very effective</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>patient_autonomy_choices</t>
+          <t>patient_decision_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>somewhat_effective</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Somewhat effective</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>patient_autonomy_choices</t>
+          <t>patient_decision_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>not_very_effective</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not very effective</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>patient_self_determination_choices</t>
+          <t>patient_consent_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very important</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>patient_self_determination_choices</t>
+          <t>patient_consent_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Somewhat important</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>patient_participation_choices</t>
+          <t>patient_consent_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not very important</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>patient_participation_choices</t>
+          <t>patient_informed_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>very_informed</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Very informed</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1617,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>somewhat_informed</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Somewhat informed</t>
         </is>
       </c>
     </row>
@@ -1726,80 +1634,80 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>not_very_informed</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not very informed</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>patient_confidentiality_choices</t>
+          <t>patient_autonomy_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very high</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>patient_confidentiality_choices</t>
+          <t>patient_autonomy_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>patient_privacy_choices</t>
+          <t>patient_autonomy_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>patient_privacy_choices</t>
+          <t>patient_self_determination_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1719,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1736,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1753,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very important</t>
         </is>
       </c>
     </row>
@@ -1862,80 +1770,284 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Somewhat important</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>patient_informed_choices</t>
+          <t>patient_participation_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Not very important</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>patient_informed_choices</t>
+          <t>patient_informed_2_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>very_informed</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Very informed</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>patient_confidentiality_choices</t>
+          <t>patient_informed_2_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>somewhat_informed</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Somewhat informed</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>patient_confidentiality_choices</t>
+          <t>patient_informed_2_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>not_very_informed</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Not very informed</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>patient_privacy_choices</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>very_high</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Very high</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>patient_privacy_choices</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>somewhat_high</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Somewhat high</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>patient_privacy_choices</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>not_very_high</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Not very high</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>patient_autonomy_2_choices</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>patient_autonomy_2_choices</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>patient_autonomy_2_choices</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>patient_self_determination_2_choices</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>patient_self_determination_2_choices</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>patient_self_determination_2_choices</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>patient_participation_2_choices</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>patient_participation_2_choices</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>patient_participation_2_choices</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
